--- a/resources/templates/vector7-plot-onboarding-template.xlsx
+++ b/resources/templates/vector7-plot-onboarding-template.xlsx
@@ -6342,6 +6342,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
@@ -6373,7 +6374,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>On the marketplace buyers see only Available, Booked or Blocked. Patta and survey numbers are never shown to buyers.</t>
+          <t>On the marketplace buyers see only Available, Booked, Sold or Blocked (other stages show as Blocked). Patta and survey numbers are never shown to buyers.</t>
         </is>
       </c>
     </row>
